--- a/prix/cecil-fongicide.xlsx
+++ b/prix/cecil-fongicide.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\peintures\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAC78B5E-B1BB-4C21-B28C-49FBF07939F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5D94B5B-DAD4-451B-9AF5-85421F491B9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
+    <workbookView xWindow="23124" yWindow="0" windowWidth="19116" windowHeight="10884" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -553,7 +553,7 @@
         <v>9</v>
       </c>
       <c r="F2" s="11">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
@@ -573,7 +573,7 @@
         <v>10</v>
       </c>
       <c r="F3" s="11">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
